--- a/output/topology_excel/9230.xlsx
+++ b/output/topology_excel/9230.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>15</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>15</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>15</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>15</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>15</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>14</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>10</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>15</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>14</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>14</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>15</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>15</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>15</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>15</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>15</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -803,13 +843,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="F17" t="n">
-        <v>285</v>
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>271</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -831,8 +877,10 @@
         <v>151</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +903,8 @@
       <c r="F19" t="n">
         <v>14</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -869,12 +919,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>90</v>
+      </c>
+      <c r="H20" t="n">
         <v>15</v>
       </c>
     </row>
@@ -899,6 +955,8 @@
       <c r="F21" t="n">
         <v>15</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +979,8 @@
       <c r="F22" t="n">
         <v>15</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1003,8 @@
       <c r="F23" t="n">
         <v>15</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1027,8 @@
       <c r="F24" t="n">
         <v>12</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1051,8 @@
       <c r="F25" t="n">
         <v>12</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1075,8 @@
       <c r="F26" t="n">
         <v>14</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1099,8 @@
       <c r="F27" t="n">
         <v>15</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1123,8 @@
       <c r="F28" t="n">
         <v>10</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1147,8 @@
       <c r="F29" t="n">
         <v>15</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1171,8 @@
       <c r="F30" t="n">
         <v>14</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
